--- a/artfynd/A 22025-2024 artfynd.xlsx
+++ b/artfynd/A 22025-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124618309</v>
+        <v>124618443</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481649</v>
+        <v>481642</v>
       </c>
       <c r="R2" t="n">
-        <v>6859183</v>
+        <v>6859198</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124618443</v>
+        <v>124618309</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481642</v>
+        <v>481649</v>
       </c>
       <c r="R3" t="n">
-        <v>6859198</v>
+        <v>6859183</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22025-2024 artfynd.xlsx
+++ b/artfynd/A 22025-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124618443</v>
+        <v>124618309</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481642</v>
+        <v>481649</v>
       </c>
       <c r="R2" t="n">
-        <v>6859198</v>
+        <v>6859183</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124618309</v>
+        <v>124618443</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481649</v>
+        <v>481642</v>
       </c>
       <c r="R3" t="n">
-        <v>6859183</v>
+        <v>6859198</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 22025-2024 artfynd.xlsx
+++ b/artfynd/A 22025-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124618443</v>
+        <v>124618309</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481642</v>
+        <v>481649</v>
       </c>
       <c r="R2" t="n">
-        <v>6859198</v>
+        <v>6859183</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124618309</v>
+        <v>124618443</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481649</v>
+        <v>481642</v>
       </c>
       <c r="R3" t="n">
-        <v>6859183</v>
+        <v>6859198</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
